--- a/data/trans_bre/P1_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 7,33</t>
+          <t>-4,18; 7,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 5,77</t>
+          <t>-3,47; 5,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 6,32</t>
+          <t>-5,27; 6,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 2,71</t>
+          <t>-9,54; 3,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-28,49; 85,73</t>
+          <t>-30,87; 80,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,44; 94,79</t>
+          <t>-35,13; 100,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 68,46</t>
+          <t>-38,42; 76,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,65; 19,51</t>
+          <t>-40,46; 24,09</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,66</t>
+          <t>-1,31; 5,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 5,61</t>
+          <t>-1,47; 4,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 3,09</t>
+          <t>-3,97; 3,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 6,04</t>
+          <t>-3,14; 6,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 102,61</t>
+          <t>-14,56; 110,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,94; 161,66</t>
+          <t>-23,32; 137,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,48; 51,16</t>
+          <t>-40,26; 55,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 49,14</t>
+          <t>-17,71; 50,3</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 6,46</t>
+          <t>-2,6; 6,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 11,3</t>
+          <t>1,27; 10,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 9,36</t>
+          <t>-0,33; 9,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 7,73</t>
+          <t>-2,88; 7,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 127,37</t>
+          <t>-31,06; 110,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,79; 206,16</t>
+          <t>10,13; 200,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 129,04</t>
+          <t>-4,64; 134,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 48,47</t>
+          <t>-13,73; 49,0</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 7,9</t>
+          <t>0,58; 8,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 3,37</t>
+          <t>-4,77; 3,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 7,66</t>
+          <t>-2,76; 6,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 2,88</t>
+          <t>-14,25; 2,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 207,1</t>
+          <t>6,08; 209,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,94; 50,4</t>
+          <t>-42,05; 44,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,81; 88,1</t>
+          <t>-20,52; 75,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,54; 15,38</t>
+          <t>-54,0; 12,74</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,82; -0,82</t>
+          <t>-10,56; -0,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 6,45</t>
+          <t>-2,55; 6,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 0,67</t>
+          <t>-12,37; 0,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,05; -2,2</t>
+          <t>-18,21; -1,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-84,71; 1,54</t>
+          <t>-83,12; -6,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-35,29; 225,95</t>
+          <t>-37,75; 232,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-66,82; 6,42</t>
+          <t>-68,8; 8,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-66,15; -11,69</t>
+          <t>-64,65; -6,58</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 8,03</t>
+          <t>-2,34; 7,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 11,13</t>
+          <t>0,6; 11,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 7,23</t>
+          <t>-3,91; 7,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,93; -0,12</t>
+          <t>-11,79; 0,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 143,8</t>
+          <t>-25,1; 132,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,22; 200,3</t>
+          <t>4,4; 215,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 81,7</t>
+          <t>-29,9; 85,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-38,18; -0,08</t>
+          <t>-39,52; 0,06</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,34</t>
+          <t>-1,67; 4,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 5,46</t>
+          <t>-1,61; 5,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 6,1</t>
+          <t>-3,14; 6,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -2,78</t>
+          <t>-14,98; -2,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 78,63</t>
+          <t>-19,88; 79,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 73,46</t>
+          <t>-14,52; 72,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 38,33</t>
+          <t>-15,64; 38,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-72,0; -15,82</t>
+          <t>-73,6; -17,43</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,82</t>
+          <t>-1,34; 3,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 2,6</t>
+          <t>-3,93; 2,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 3,07</t>
+          <t>-3,46; 3,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,82; 14,78</t>
+          <t>3,95; 15,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 78,0</t>
+          <t>-19,96; 74,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,65; 28,16</t>
+          <t>-32,4; 25,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,81; 28,48</t>
+          <t>-24,97; 27,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>27,47; 311,22</t>
+          <t>28,46; 282,95</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,76</t>
+          <t>0,03; 2,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,96</t>
+          <t>0,26; 3,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,34</t>
+          <t>-1,05; 2,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 2,69</t>
+          <t>-3,66; 2,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,9; 42,4</t>
+          <t>0,63; 42,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 38,39</t>
+          <t>3,2; 41,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 20,38</t>
+          <t>-7,64; 20,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 18,47</t>
+          <t>-20,14; 19,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,5</t>
+          <t>-3,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-14,15%</t>
+          <t>-18,37%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 7,13</t>
+          <t>-3,93; 7,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 5,95</t>
+          <t>-3,45; 5,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 6,54</t>
+          <t>-5,22; 6,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 3,27</t>
+          <t>-9,11; 2,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 80,92</t>
+          <t>-29,28; 91,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 100,3</t>
+          <t>-35,94; 97,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 76,18</t>
+          <t>-36,05; 68,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,46; 24,09</t>
+          <t>-41,76; 16,66</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 5,76</t>
+          <t>-1,44; 5,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,94</t>
+          <t>-1,37; 5,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 3,45</t>
+          <t>-3,78; 3,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 6,18</t>
+          <t>-4,34; 5,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 110,77</t>
+          <t>-18,6; 100,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 137,45</t>
+          <t>-23,6; 138,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 55,47</t>
+          <t>-39,62; 53,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 50,3</t>
+          <t>-22,84; 38,6</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 6,01</t>
+          <t>-2,32; 5,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,64</t>
+          <t>1,21; 11,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 9,44</t>
+          <t>-0,37; 9,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 7,8</t>
+          <t>-3,62; 6,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 110,33</t>
+          <t>-27,64; 115,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,13; 200,79</t>
+          <t>11,14; 200,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 134,66</t>
+          <t>-5,96; 131,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 49,0</t>
+          <t>-15,9; 41,6</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,46</t>
+          <t>-1,47</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-20,65%</t>
+          <t>-6,49%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 8,29</t>
+          <t>0,23; 7,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 3,42</t>
+          <t>-5,25; 3,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 6,83</t>
+          <t>-2,79; 7,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 2,31</t>
+          <t>-7,51; 4,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,08; 209,83</t>
+          <t>-0,49; 203,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,05; 44,08</t>
+          <t>-44,22; 44,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 75,44</t>
+          <t>-21,18; 95,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,0; 12,74</t>
+          <t>-28,15; 25,83</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-8,82</t>
+          <t>-5,62</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-35,67%</t>
+          <t>-22,68%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,56; -0,91</t>
+          <t>-10,83; -0,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 6,84</t>
+          <t>-1,83; 7,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 0,69</t>
+          <t>-12,07; 0,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,21; -1,46</t>
+          <t>-12,14; 0,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-83,12; -6,01</t>
+          <t>-83,67; -0,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,75; 232,41</t>
+          <t>-31,7; 263,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-68,8; 8,51</t>
+          <t>-67,18; 13,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-64,65; -6,58</t>
+          <t>-41,2; 3,79</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-6,08</t>
+          <t>-6,0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-22,61%</t>
+          <t>-22,02%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 7,83</t>
+          <t>-1,81; 8,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 11,08</t>
+          <t>0,71; 11,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 7,46</t>
+          <t>-3,85; 8,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 0,01</t>
+          <t>-11,91; -0,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 132,17</t>
+          <t>-18,71; 137,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,4; 215,93</t>
+          <t>4,7; 217,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 85,2</t>
+          <t>-28,53; 94,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-39,52; 0,06</t>
+          <t>-39,46; -1,4</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-7,2</t>
+          <t>-4,38</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-41,1%</t>
+          <t>-24,32%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 4,35</t>
+          <t>-1,9; 4,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 5,39</t>
+          <t>-1,52; 5,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 6,13</t>
+          <t>-2,85; 5,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,98; -2,85</t>
+          <t>-8,51; -0,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 79,03</t>
+          <t>-23,92; 75,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 72,22</t>
+          <t>-14,31; 70,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 38,96</t>
+          <t>-13,8; 35,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-73,6; -17,43</t>
+          <t>-40,31; -3,75</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,67</t>
+          <t>4,57</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,72</t>
+          <t>-1,3; 3,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 2,27</t>
+          <t>-4,29; 2,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 3,09</t>
+          <t>-3,66; 3,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,95; 15,18</t>
+          <t>1,29; 8,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 74,77</t>
+          <t>-17,62; 77,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 25,53</t>
+          <t>-35,26; 26,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 27,87</t>
+          <t>-25,47; 30,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,46; 282,95</t>
+          <t>8,09; 68,91</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-3,08%</t>
+          <t>-4,51%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,73</t>
+          <t>0,07; 2,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,11</t>
+          <t>0,1; 2,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,43</t>
+          <t>-0,88; 2,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 2,82</t>
+          <t>-2,5; 0,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 42,5</t>
+          <t>0,89; 44,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,2; 41,48</t>
+          <t>1,07; 39,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 20,78</t>
+          <t>-6,68; 20,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 19,67</t>
+          <t>-13,0; 4,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Población que conforma un hogar unipersonal</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
